--- a/artfynd/A 45017-2025 artfynd.xlsx
+++ b/artfynd/A 45017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>60949</v>
       </c>
       <c r="B2" t="n">
-        <v>57586</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542067.4822411647</v>
+        <v>542067</v>
       </c>
       <c r="R2" t="n">
-        <v>6234207.031024022</v>
+        <v>6234207</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -757,19 +752,9 @@
           <t>2009-05-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-05-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,42 +785,33 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86188463</v>
+        <v>86188498</v>
       </c>
       <c r="B3" t="n">
-        <v>101693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224417</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk solvända</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. obscurum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Celak.) Holub</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542040.7758884176</v>
+        <v>542071</v>
       </c>
       <c r="R3" t="n">
-        <v>6234205.656954549</v>
+        <v>6234235</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,24 +861,9 @@
           <t>2020-06-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gröna bladundersidor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,38 +891,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86188498</v>
+        <v>86188463</v>
       </c>
       <c r="B4" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>224417</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Mörk solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Helianthemum nummularium subsp. obscurum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Celak.) Holub</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -978,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542070.5427655309</v>
+        <v>542041</v>
       </c>
       <c r="R4" t="n">
-        <v>6234235.392033016</v>
+        <v>6234206</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,19 +971,14 @@
           <t>2020-06-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gröna bladundersidor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,6 +1003,109 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86188469</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bokahultet, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>542041</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6234206</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rödeby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niclas Wahlgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Niclas Wahlgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45017-2025 artfynd.xlsx
+++ b/artfynd/A 45017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60949</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86188498</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86188463</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,8 +1126,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86188469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>